--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556315039</v>
+        <v>46157.93116142491</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116142491</v>
+        <v>46157.93139093051</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93139093051</v>
+        <v>46157.93385924643</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93385924643</v>
+        <v>46157.93697100691</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93697100691</v>
+        <v>46158.28205892436</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205892436</v>
+        <v>46158.29654530734</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29654530734</v>
+        <v>46158.29809683758</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809683758</v>
+        <v>46158.33372074686</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33372074686</v>
+        <v>46158.37223967387</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Июнь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37223967387</v>
+        <v>46158.37276493135</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
